--- a/APPT/data/output/Final_Production_Plan_2026-01-21.xlsx
+++ b/APPT/data/output/Final_Production_Plan_2026-01-21.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2185" uniqueCount="409">
   <si>
     <t>Production Line</t>
   </si>
@@ -247,88 +247,88 @@
     <t>H&amp;S SS 2in1</t>
   </si>
   <si>
-    <t>CI630</t>
-  </si>
-  <si>
-    <t>CI631</t>
-  </si>
-  <si>
-    <t>CI632</t>
+    <t>CI645</t>
+  </si>
+  <si>
+    <t>CI646</t>
+  </si>
+  <si>
+    <t>CI647</t>
   </si>
   <si>
     <t>REP01-0121</t>
   </si>
   <si>
-    <t>CI633</t>
-  </si>
-  <si>
-    <t>CI635</t>
-  </si>
-  <si>
-    <t>CI636</t>
+    <t>CI648</t>
+  </si>
+  <si>
+    <t>CI650</t>
+  </si>
+  <si>
+    <t>CI651</t>
   </si>
   <si>
     <t>REP02-0121</t>
   </si>
   <si>
-    <t>CI638</t>
-  </si>
-  <si>
-    <t>CI639</t>
-  </si>
-  <si>
-    <t>CI640</t>
-  </si>
-  <si>
-    <t>CI642</t>
-  </si>
-  <si>
-    <t>CI644</t>
-  </si>
-  <si>
-    <t>CI645</t>
-  </si>
-  <si>
-    <t>CI647</t>
-  </si>
-  <si>
-    <t>CI648</t>
+    <t>CI653</t>
+  </si>
+  <si>
+    <t>CI654</t>
+  </si>
+  <si>
+    <t>CI655</t>
+  </si>
+  <si>
+    <t>CI657</t>
+  </si>
+  <si>
+    <t>CI659</t>
+  </si>
+  <si>
+    <t>CI660</t>
+  </si>
+  <si>
+    <t>CI662</t>
+  </si>
+  <si>
+    <t>CI663</t>
+  </si>
+  <si>
+    <t>CI664</t>
+  </si>
+  <si>
+    <t>REP03-0121</t>
+  </si>
+  <si>
+    <t>CI665</t>
+  </si>
+  <si>
+    <t>CI666</t>
+  </si>
+  <si>
+    <t>CI667</t>
+  </si>
+  <si>
+    <t>CI668</t>
+  </si>
+  <si>
+    <t>CI669</t>
   </si>
   <si>
     <t>CI649</t>
   </si>
   <si>
-    <t>REP03-0121</t>
-  </si>
-  <si>
-    <t>CI650</t>
-  </si>
-  <si>
-    <t>CI651</t>
-  </si>
-  <si>
     <t>CI652</t>
   </si>
   <si>
-    <t>CI653</t>
-  </si>
-  <si>
-    <t>CI654</t>
-  </si>
-  <si>
-    <t>CI634</t>
-  </si>
-  <si>
-    <t>CI637</t>
-  </si>
-  <si>
-    <t>CI641</t>
-  </si>
-  <si>
-    <t>CI643</t>
-  </si>
-  <si>
-    <t>CI646</t>
+    <t>CI656</t>
+  </si>
+  <si>
+    <t>CI658</t>
+  </si>
+  <si>
+    <t>CI661</t>
   </si>
   <si>
     <t>21422079</t>
@@ -382,10 +382,7 @@
     <t>B</t>
   </si>
   <si>
-    <t>TK#_6_# [Wash 20m] + TK#_2_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_20_# [Wash 20m] + TK#_9_# [Wash 20m]</t>
+    <t>TK#_8_# [Wash 20m] + TK#_27_# [Wash 20m]</t>
   </si>
   <si>
     <t>NO_TANK_AVAILABLE</t>
@@ -394,43 +391,40 @@
     <t>HC Base Tank</t>
   </si>
   <si>
-    <t>TK#_8_# + TK#_9_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_7_# [Wash 20m] + TK#_6_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_21_# + TK#_28_#</t>
-  </si>
-  <si>
-    <t>TK#_20_# [Wash 20m] + TK#_19_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_27_# [Wash 20m] + TK#_25_# [Wash 20m]</t>
+    <t>TK#_27_# [Wash 20m] + TK#_28_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_8_# [Wash 20m] + TK#_6_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_7_# + TK#_19_#</t>
+  </si>
+  <si>
+    <t>TK#_20_# [Wash 20m] + TK#_1_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_5_# [Wash 20m] + TK#_24_# [Wash 20m]</t>
   </si>
   <si>
     <t>TK#_53_# [Wash 20m]</t>
   </si>
   <si>
-    <t>TK#_7_# + TK#_6_#</t>
+    <t>TK#_8_# + TK#_6_#</t>
   </si>
   <si>
     <t>TK#_53_#</t>
   </si>
   <si>
-    <t>TK#_6_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_20_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_2_#</t>
-  </si>
-  <si>
-    <t>TK#_3_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_15_# [Wash 20m]</t>
+    <t>TK#_8_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_18_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_25_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_16_# [Wash 20m]</t>
   </si>
   <si>
     <t>LOW: SLS</t>
@@ -787,13 +781,13 @@
     <t>C</t>
   </si>
   <si>
-    <t>CI630: H&amp;S SS</t>
-  </si>
-  <si>
-    <t>CI631: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI632: H&amp;S Daily Clean Libra</t>
+    <t>CI645: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>CI646: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI647: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
     <t>WASHOUT</t>
@@ -802,79 +796,82 @@
     <t>REP01-0121: HC BASE</t>
   </si>
   <si>
-    <t>CI633: H&amp;S Menthol Fresh</t>
-  </si>
-  <si>
-    <t>CI635: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI636: H&amp;S Daily Clean Libra</t>
+    <t>CI648: H&amp;S Menthol Fresh</t>
+  </si>
+  <si>
+    <t>CI650: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI651: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
     <t>REP02-0121: HC BASE</t>
   </si>
   <si>
-    <t>CI638: H&amp;S AHF</t>
-  </si>
-  <si>
-    <t>CI639: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI640: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI642: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI644: H&amp;S SS</t>
-  </si>
-  <si>
-    <t>CI645: H&amp;S Menthol Fresh</t>
-  </si>
-  <si>
-    <t>CI647: H&amp;S Daily Smooth Libra</t>
-  </si>
-  <si>
-    <t>CI648: H&amp;S SS</t>
-  </si>
-  <si>
-    <t>CI649: H&amp;S Daily Clean Libra</t>
+    <t>CI653: H&amp;S AHF</t>
+  </si>
+  <si>
+    <t>CI654: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI655: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI657: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI659: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>CI660: H&amp;S Menthol Fresh</t>
+  </si>
+  <si>
+    <t>CI662: H&amp;S Daily Smooth Libra</t>
+  </si>
+  <si>
+    <t>CI663: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>CI664: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
     <t>REP03-0121: HC BASE</t>
   </si>
   <si>
-    <t>CI650: H&amp;S SS</t>
-  </si>
-  <si>
-    <t>CI651: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI652: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI653: H&amp;S SS</t>
-  </si>
-  <si>
-    <t>CI654: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI634: H&amp;S CM</t>
-  </si>
-  <si>
-    <t>CI637: H&amp;S AP 2in1</t>
-  </si>
-  <si>
-    <t>CI641: H&amp;S SS</t>
-  </si>
-  <si>
-    <t>CI643: H&amp;S SS 2in1</t>
-  </si>
-  <si>
-    <t>CI646: H&amp;S SS</t>
-  </si>
-  <si>
-    <t>TK#_3_#</t>
+    <t>CI665: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>CI666: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI667: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI668: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>CI669: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI649: H&amp;S CM</t>
+  </si>
+  <si>
+    <t>CI652: H&amp;S AP 2in1</t>
+  </si>
+  <si>
+    <t>CI656: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>CI658: H&amp;S SS 2in1</t>
+  </si>
+  <si>
+    <t>CI661: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>TK#_1_#</t>
+  </si>
+  <si>
+    <t>TK#_5_#</t>
   </si>
   <si>
     <t>TK#_6_#</t>
@@ -886,10 +883,10 @@
     <t>TK#_8_#</t>
   </si>
   <si>
-    <t>TK#_9_#</t>
-  </si>
-  <si>
-    <t>TK#_15_#</t>
+    <t>TK#_16_#</t>
+  </si>
+  <si>
+    <t>TK#_18_#</t>
   </si>
   <si>
     <t>TK#_19_#</t>
@@ -898,7 +895,7 @@
     <t>TK#_20_#</t>
   </si>
   <si>
-    <t>TK#_21_#</t>
+    <t>TK#_24_#</t>
   </si>
   <si>
     <t>TK#_25_#</t>
@@ -1168,49 +1165,46 @@
     <t>2026-01-24 13:00</t>
   </si>
   <si>
-    <t>CI630: H&amp;S SS | CI634: H&amp;S CM</t>
-  </si>
-  <si>
-    <t>WASHOUT (20m) | CI634: H&amp;S CM</t>
-  </si>
-  <si>
-    <t>CI640: H&amp;S Daily Clean Libra | CI634: H&amp;S CM</t>
-  </si>
-  <si>
-    <t>CI640: H&amp;S Daily Clean Libra | CI649: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI649: H&amp;S Daily Clean Libra | WASHOUT (20m)</t>
-  </si>
-  <si>
-    <t>CI649: H&amp;S Daily Clean Libra | CI651: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI651: H&amp;S Daily Cool Libra | CI654: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
     <t>WASHOUT (20m)</t>
   </si>
   <si>
-    <t>CI631: H&amp;S Daily Clean Libra | WASHOUT (20m)</t>
-  </si>
-  <si>
-    <t>CI631: H&amp;S Daily Clean Libra | CI638: H&amp;S AHF</t>
-  </si>
-  <si>
-    <t>CI631: H&amp;S Daily Clean Libra | CI637: H&amp;S AP 2in1</t>
-  </si>
-  <si>
-    <t>WASHOUT (20m) | CI637: H&amp;S AP 2in1</t>
-  </si>
-  <si>
-    <t>CI644: H&amp;S SS | CI637: H&amp;S AP 2in1</t>
-  </si>
-  <si>
-    <t>CI648: H&amp;S SS | CI650: H&amp;S SS</t>
-  </si>
-  <si>
-    <t>CI650: H&amp;S SS | CI653: H&amp;S SS</t>
+    <t>CI655: H&amp;S Daily Clean Libra | CI664: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI664: H&amp;S Daily Clean Libra | WASHOUT (20m)</t>
+  </si>
+  <si>
+    <t>CI664: H&amp;S Daily Clean Libra | CI666: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI666: H&amp;S Daily Cool Libra | CI669: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI645: H&amp;S SS | CI649: H&amp;S CM</t>
+  </si>
+  <si>
+    <t>WASHOUT (20m) | CI649: H&amp;S CM</t>
+  </si>
+  <si>
+    <t>CI655: H&amp;S Daily Clean Libra | CI649: H&amp;S CM</t>
+  </si>
+  <si>
+    <t>CI652: H&amp;S AP 2in1 | WASHOUT (20m)</t>
+  </si>
+  <si>
+    <t>CI652: H&amp;S AP 2in1 | CI661: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>CI645: H&amp;S SS | WASHOUT (20m)</t>
+  </si>
+  <si>
+    <t>CI645: H&amp;S SS | CI653: H&amp;S AHF</t>
+  </si>
+  <si>
+    <t>CI663: H&amp;S SS | CI665: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>CI665: H&amp;S SS | CI668: H&amp;S SS</t>
   </si>
   <si>
     <t>Sr.No</t>
@@ -1735,7 +1729,7 @@
         <v>46043.50069444445</v>
       </c>
       <c r="S2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1794,7 +1788,7 @@
         <v>46043.54722222222</v>
       </c>
       <c r="S3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1844,7 +1838,7 @@
         <v>1083</v>
       </c>
       <c r="P4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q4" s="2">
         <v>46043.37708333333</v>
@@ -1853,7 +1847,7 @@
         <v>46043.59027777778</v>
       </c>
       <c r="S4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1903,7 +1897,7 @@
         <v>980</v>
       </c>
       <c r="P5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q5" s="2">
         <v>46043.38194444445</v>
@@ -1912,7 +1906,7 @@
         <v>46043.42361111111</v>
       </c>
       <c r="S5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1962,7 +1956,7 @@
         <v>890</v>
       </c>
       <c r="P6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q6" s="2">
         <v>46043.39583333334</v>
@@ -1971,7 +1965,7 @@
         <v>46044.31944444445</v>
       </c>
       <c r="S6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2021,7 +2015,7 @@
         <v>1018</v>
       </c>
       <c r="P7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q7" s="2">
         <v>46043.54722222222</v>
@@ -2030,7 +2024,7 @@
         <v>46043.73055555556</v>
       </c>
       <c r="S7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2080,7 +2074,7 @@
         <v>990</v>
       </c>
       <c r="P8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q8" s="2">
         <v>46043.59027777778</v>
@@ -2089,7 +2083,7 @@
         <v>46043.80416666667</v>
       </c>
       <c r="S8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2139,7 +2133,7 @@
         <v>1050</v>
       </c>
       <c r="P9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q9" s="2">
         <v>46043.70833333334</v>
@@ -2148,7 +2142,7 @@
         <v>46043.75</v>
       </c>
       <c r="S9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2198,7 +2192,7 @@
         <v>465</v>
       </c>
       <c r="P10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q10" s="2">
         <v>46043.71180555555</v>
@@ -2207,7 +2201,7 @@
         <v>46043.83194444444</v>
       </c>
       <c r="S10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2257,7 +2251,7 @@
         <v>382</v>
       </c>
       <c r="P11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q11" s="2">
         <v>46043.73055555556</v>
@@ -2266,7 +2260,7 @@
         <v>46043.91458333333</v>
       </c>
       <c r="S11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2316,7 +2310,7 @@
         <v>398</v>
       </c>
       <c r="P12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q12" s="2">
         <v>46043.80416666667</v>
@@ -2325,7 +2319,7 @@
         <v>46044.35069444445</v>
       </c>
       <c r="S12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2375,7 +2369,7 @@
         <v>467</v>
       </c>
       <c r="P13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q13" s="2">
         <v>46043.91458333333</v>
@@ -2384,7 +2378,7 @@
         <v>46044.43125</v>
       </c>
       <c r="S13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2434,7 +2428,7 @@
         <v>806</v>
       </c>
       <c r="P14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q14" s="2">
         <v>46044.2125</v>
@@ -2443,7 +2437,7 @@
         <v>46044.33263888889</v>
       </c>
       <c r="S14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2493,7 +2487,7 @@
         <v>870</v>
       </c>
       <c r="P15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q15" s="2">
         <v>46044.31944444445</v>
@@ -2502,7 +2496,7 @@
         <v>46046.38958333333</v>
       </c>
       <c r="S15" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2552,7 +2546,7 @@
         <v>825</v>
       </c>
       <c r="P16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q16" s="2">
         <v>46044.35069444445</v>
@@ -2561,7 +2555,7 @@
         <v>46044.56458333333</v>
       </c>
       <c r="S16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2611,7 +2605,7 @@
         <v>740</v>
       </c>
       <c r="P17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q17" s="2">
         <v>46044.35416666666</v>
@@ -2620,7 +2614,7 @@
         <v>46044.54236111111</v>
       </c>
       <c r="S17" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -2670,7 +2664,7 @@
         <v>761</v>
       </c>
       <c r="P18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q18" s="2">
         <v>46044.43125</v>
@@ -2679,7 +2673,7 @@
         <v>46044.61527777778</v>
       </c>
       <c r="S18" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -2729,7 +2723,7 @@
         <v>676</v>
       </c>
       <c r="P19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q19" s="2">
         <v>46044.44861111111</v>
@@ -2738,7 +2732,7 @@
         <v>46044.49027777778</v>
       </c>
       <c r="S19" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -2788,7 +2782,7 @@
         <v>195</v>
       </c>
       <c r="P20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q20" s="2">
         <v>46044.54236111111</v>
@@ -2797,7 +2791,7 @@
         <v>46044.73125</v>
       </c>
       <c r="S20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -2847,7 +2841,7 @@
         <v>137</v>
       </c>
       <c r="P21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q21" s="2">
         <v>46044.56458333333</v>
@@ -2856,7 +2850,7 @@
         <v>46044.77777777778</v>
       </c>
       <c r="S21" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -2906,7 +2900,7 @@
         <v>120</v>
       </c>
       <c r="P22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q22" s="2">
         <v>46044.61527777778</v>
@@ -2915,7 +2909,7 @@
         <v>46044.79861111111</v>
       </c>
       <c r="S22" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -2965,7 +2959,7 @@
         <v>143</v>
       </c>
       <c r="P23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q23" s="2">
         <v>46044.73125</v>
@@ -2974,7 +2968,7 @@
         <v>46046.33055555556</v>
       </c>
       <c r="S23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3024,7 +3018,7 @@
         <v>120</v>
       </c>
       <c r="P24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q24" s="2">
         <v>46044.77777777778</v>
@@ -3033,7 +3027,7 @@
         <v>46046.47083333333</v>
       </c>
       <c r="S24" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3083,7 +3077,7 @@
         <v>181</v>
       </c>
       <c r="P25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q25" s="2">
         <v>46043.50069444445</v>
@@ -3092,7 +3086,7 @@
         <v>46043.59513888889</v>
       </c>
       <c r="S25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -3142,7 +3136,7 @@
         <v>250</v>
       </c>
       <c r="P26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q26" s="2">
         <v>46043.625</v>
@@ -3151,7 +3145,7 @@
         <v>46043.71180555555</v>
       </c>
       <c r="S26" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -3201,7 +3195,7 @@
         <v>438</v>
       </c>
       <c r="P27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q27" s="2">
         <v>46043.83194444444</v>
@@ -3210,7 +3204,7 @@
         <v>46044.06527777778</v>
       </c>
       <c r="S27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -3260,7 +3254,7 @@
         <v>664</v>
       </c>
       <c r="P28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q28" s="2">
         <v>46044.06527777778</v>
@@ -3269,7 +3263,7 @@
         <v>46044.2125</v>
       </c>
       <c r="S28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -3319,7 +3313,7 @@
         <v>939</v>
       </c>
       <c r="P29" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="Q29" s="2">
         <v>46044.33263888889</v>
@@ -3328,7 +3322,7 @@
         <v>46044.35763888889</v>
       </c>
       <c r="S29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -3348,7 +3342,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -3360,12 +3354,12 @@
         <v>114</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
         <v>119</v>
@@ -3373,958 +3367,958 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
         <v>119</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B4" t="s">
         <v>119</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s">
         <v>119</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
         <v>119</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B7" t="s">
         <v>119</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B8" t="s">
         <v>119</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B9" t="s">
         <v>119</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B10" t="s">
         <v>119</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s">
         <v>119</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s">
         <v>119</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s">
         <v>120</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s">
         <v>120</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B15" t="s">
         <v>120</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B16" t="s">
         <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B17" t="s">
         <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s">
         <v>120</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B19" t="s">
         <v>120</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B20" t="s">
         <v>120</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
         <v>120</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B22" t="s">
         <v>120</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s">
         <v>120</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B24" t="s">
         <v>120</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B25" t="s">
         <v>120</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s">
         <v>120</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B27" t="s">
         <v>120</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B28" t="s">
         <v>120</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B30" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B32" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B33" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B34" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B35" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B37" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B38" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B39" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B40" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B41" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B42" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B43" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B44" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B45" t="s">
         <v>119</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B46" t="s">
         <v>119</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B47" t="s">
         <v>119</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B48" t="s">
         <v>119</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B49" t="s">
         <v>119</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B50" t="s">
         <v>119</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B51" t="s">
         <v>119</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B52" t="s">
         <v>119</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B53" t="s">
         <v>119</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B54" t="s">
         <v>119</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B55" t="s">
         <v>119</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B56" t="s">
         <v>119</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B57" t="s">
         <v>119</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B58" t="s">
         <v>119</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B59" t="s">
         <v>119</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B60" t="s">
         <v>119</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B61" t="s">
         <v>120</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B62" t="s">
         <v>120</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B63" t="s">
         <v>120</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B64" t="s">
         <v>120</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B65" t="s">
         <v>120</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B66" t="s">
         <v>120</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B67" t="s">
         <v>120</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B68" t="s">
         <v>120</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B69" t="s">
         <v>120</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B70" t="s">
         <v>120</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B71" t="s">
         <v>120</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B72" t="s">
         <v>120</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B73" t="s">
         <v>120</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B74" t="s">
         <v>120</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B75" t="s">
         <v>120</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B76" t="s">
         <v>120</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B77" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B78" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B79" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B80" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B81" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B82" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B83" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B84" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B85" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B86" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B87" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B88" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B89" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B90" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B91" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B92" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B93" t="s">
         <v>119</v>
@@ -4332,7 +4326,7 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B94" t="s">
         <v>119</v>
@@ -4340,106 +4334,106 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B95" t="s">
         <v>119</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B96" t="s">
         <v>119</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B97" t="s">
         <v>119</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B98" t="s">
         <v>119</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B99" t="s">
         <v>119</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B100" t="s">
         <v>119</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B101" t="s">
         <v>119</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B102" t="s">
         <v>119</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B103" t="s">
         <v>119</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B104" t="s">
         <v>119</v>
@@ -4447,7 +4441,7 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B105" t="s">
         <v>119</v>
@@ -4455,73 +4449,73 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B106" t="s">
         <v>119</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B107" t="s">
         <v>119</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B108" t="s">
         <v>119</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B109" t="s">
         <v>120</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B110" t="s">
         <v>120</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B111" t="s">
         <v>120</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B112" t="s">
         <v>120</v>
@@ -4529,7 +4523,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B113" t="s">
         <v>120</v>
@@ -4537,7 +4531,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B114" t="s">
         <v>120</v>
@@ -4560,57 +4554,57 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>135</v>
+        <v>283</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
         <v>119</v>
@@ -4618,7 +4612,7 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
         <v>119</v>
@@ -4626,4487 +4620,4232 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
         <v>119</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>256</v>
+      <c r="G4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>256</v>
+      <c r="G5" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>256</v>
+      <c r="G6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B7" t="s">
         <v>119</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>257</v>
+      <c r="G7" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>257</v>
+      <c r="G8" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>257</v>
+      <c r="G9" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B10" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>257</v>
+      <c r="G10" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s">
         <v>120</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>257</v>
+      <c r="G11" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>257</v>
+      <c r="G12" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>257</v>
+      <c r="G13" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s">
         <v>120</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>257</v>
+      <c r="G14" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B15" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>257</v>
+      <c r="G15" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
         <v>158</v>
       </c>
-      <c r="B16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
+      <c r="B18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
         <v>159</v>
       </c>
-      <c r="B17" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
+      <c r="B19" t="s">
+        <v>120</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
         <v>160</v>
       </c>
-      <c r="B18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
+      <c r="B20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
         <v>161</v>
       </c>
-      <c r="B19" t="s">
-        <v>120</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
+      <c r="B21" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
         <v>162</v>
       </c>
-      <c r="B20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
+      <c r="B22" t="s">
+        <v>120</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
         <v>163</v>
       </c>
-      <c r="B21" t="s">
-        <v>120</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
+      <c r="B23" t="s">
+        <v>120</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
         <v>164</v>
       </c>
-      <c r="B22" t="s">
-        <v>120</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
+      <c r="B24" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
         <v>165</v>
       </c>
-      <c r="B23" t="s">
-        <v>120</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
+      <c r="B25" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
         <v>166</v>
       </c>
-      <c r="B24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
+      <c r="B26" t="s">
+        <v>120</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
         <v>167</v>
       </c>
-      <c r="B25" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" t="s">
+      <c r="B27" t="s">
+        <v>253</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
         <v>168</v>
       </c>
-      <c r="B26" t="s">
-        <v>120</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" t="s">
+      <c r="B28" t="s">
+        <v>253</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
         <v>169</v>
       </c>
-      <c r="B27" t="s">
-        <v>255</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" t="s">
+      <c r="B29" t="s">
+        <v>253</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
         <v>170</v>
       </c>
-      <c r="B28" t="s">
-        <v>255</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" t="s">
+      <c r="B30" t="s">
+        <v>253</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
         <v>171</v>
       </c>
-      <c r="B29" t="s">
-        <v>255</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" t="s">
+      <c r="B31" t="s">
+        <v>253</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
         <v>172</v>
       </c>
-      <c r="B30" t="s">
-        <v>255</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" t="s">
+      <c r="B32" t="s">
+        <v>253</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" t="s">
         <v>173</v>
       </c>
-      <c r="B31" t="s">
-        <v>255</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" t="s">
+      <c r="B33" t="s">
+        <v>253</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" t="s">
         <v>174</v>
       </c>
-      <c r="B32" t="s">
-        <v>255</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" t="s">
+      <c r="B34" t="s">
+        <v>253</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" t="s">
         <v>175</v>
       </c>
-      <c r="B33" t="s">
-        <v>255</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" t="s">
+      <c r="B35" t="s">
+        <v>253</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" t="s">
         <v>176</v>
       </c>
-      <c r="B34" t="s">
-        <v>255</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" t="s">
+      <c r="B36" t="s">
+        <v>253</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" t="s">
         <v>177</v>
       </c>
-      <c r="B35" t="s">
-        <v>255</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" t="s">
+      <c r="B37" t="s">
+        <v>253</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" t="s">
         <v>178</v>
       </c>
-      <c r="B36" t="s">
-        <v>255</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" t="s">
+      <c r="B38" t="s">
+        <v>253</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" t="s">
         <v>179</v>
       </c>
-      <c r="B37" t="s">
-        <v>255</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" t="s">
+      <c r="B39" t="s">
+        <v>253</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" t="s">
         <v>180</v>
       </c>
-      <c r="B38" t="s">
-        <v>255</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" t="s">
+      <c r="B40" t="s">
+        <v>253</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" t="s">
         <v>181</v>
       </c>
-      <c r="B39" t="s">
-        <v>255</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" t="s">
+      <c r="B41" t="s">
+        <v>253</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" t="s">
         <v>182</v>
       </c>
-      <c r="B40" t="s">
-        <v>255</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" t="s">
+      <c r="B42" t="s">
+        <v>253</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" t="s">
         <v>183</v>
       </c>
-      <c r="B41" t="s">
-        <v>255</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" t="s">
+      <c r="B43" t="s">
+        <v>119</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" t="s">
         <v>184</v>
       </c>
-      <c r="B42" t="s">
-        <v>255</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" t="s">
+      <c r="B44" t="s">
+        <v>119</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" t="s">
         <v>185</v>
       </c>
-      <c r="B43" t="s">
-        <v>119</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" t="s">
+      <c r="B45" t="s">
+        <v>119</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" t="s">
         <v>186</v>
       </c>
-      <c r="B44" t="s">
-        <v>119</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" t="s">
+      <c r="B46" t="s">
+        <v>119</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" t="s">
         <v>187</v>
       </c>
-      <c r="B45" t="s">
-        <v>119</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" t="s">
+      <c r="B47" t="s">
+        <v>119</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" t="s">
         <v>188</v>
       </c>
-      <c r="B46" t="s">
-        <v>119</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" t="s">
-        <v>189</v>
-      </c>
-      <c r="B47" t="s">
-        <v>119</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
-      <c r="A48" t="s">
-        <v>190</v>
-      </c>
       <c r="B48" t="s">
         <v>119</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>383</v>
-      </c>
       <c r="G48" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>257</v>
+        <v>387</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B49" t="s">
         <v>119</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>383</v>
-      </c>
       <c r="G49" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>391</v>
+        <v>387</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B50" t="s">
         <v>119</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>383</v>
-      </c>
       <c r="G50" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="K50" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="N50" s="3" t="s">
         <v>393</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B51" t="s">
         <v>119</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>383</v>
-      </c>
       <c r="G51" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="K51" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="N51" s="3" t="s">
         <v>393</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="52" spans="1:15">
       <c r="A52" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B52" t="s">
         <v>119</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>383</v>
-      </c>
       <c r="G52" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="K52" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="N52" s="3" t="s">
         <v>393</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="53" spans="1:15">
       <c r="A53" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B53" t="s">
         <v>119</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>393</v>
+        <v>388</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B54" t="s">
         <v>119</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="E54" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B55" t="s">
         <v>119</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="E55" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>281</v>
+        <v>389</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B56" t="s">
         <v>119</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="E56" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>281</v>
+        <v>389</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B57" t="s">
         <v>119</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>283</v>
-      </c>
       <c r="E57" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>265</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K57" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>268</v>
+      <c r="I57" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="58" spans="1:15">
       <c r="A58" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B58" t="s">
         <v>119</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>283</v>
-      </c>
       <c r="E58" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>265</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K58" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>268</v>
+      <c r="I58" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B59" t="s">
         <v>120</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>283</v>
+        <v>382</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>265</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>265</v>
+        <v>281</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>390</v>
+        <v>266</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>268</v>
+        <v>382</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="60" spans="1:15">
       <c r="A60" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B60" t="s">
         <v>120</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>265</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>390</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="61" spans="1:15">
       <c r="A61" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B61" t="s">
         <v>120</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>265</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>284</v>
+        <v>391</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="62" spans="1:15">
       <c r="A62" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s">
         <v>120</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>265</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>284</v>
+        <v>391</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B63" t="s">
         <v>120</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>265</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L63" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="64" spans="1:15">
       <c r="A64" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B64" t="s">
         <v>120</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>265</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B65" t="s">
         <v>120</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>283</v>
+        <v>382</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>265</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>268</v>
+        <v>382</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>390</v>
+        <v>280</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>390</v>
+        <v>263</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B66" t="s">
         <v>120</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>265</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J66" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L66" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M66" s="3" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="67" spans="1:16">
       <c r="A67" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B67" t="s">
         <v>120</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>265</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J67" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L67" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K67" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M67" s="3" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="68" spans="1:16">
       <c r="A68" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B68" t="s">
         <v>120</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I68" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E68" s="3" t="s">
+      <c r="J68" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="J68" s="3" t="s">
+      <c r="L68" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K68" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M68" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N68" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O68" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B69" t="s">
         <v>120</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I69" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E69" s="3" t="s">
+      <c r="J69" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="J69" s="3" t="s">
+      <c r="L69" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K69" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M69" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N69" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O69" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B70" t="s">
         <v>120</v>
       </c>
       <c r="C70" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I70" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E70" s="3" t="s">
+      <c r="J70" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K70" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="J70" s="3" t="s">
+      <c r="L70" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K70" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L70" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M70" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N70" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O70" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B71" t="s">
         <v>120</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I71" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E71" s="3" t="s">
+      <c r="J71" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K71" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="J71" s="3" t="s">
+      <c r="L71" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K71" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L71" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M71" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N71" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O71" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B72" t="s">
         <v>120</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="J72" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L72" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M72" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B73" t="s">
         <v>120</v>
       </c>
       <c r="C73" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I73" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="J73" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L73" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K73" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L73" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M73" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N73" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O73" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="74" spans="1:16">
       <c r="A74" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B74" t="s">
         <v>120</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I74" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="J74" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L74" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K74" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L74" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M74" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N74" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O74" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="75" spans="1:16">
       <c r="A75" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B75" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I75" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="J75" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L75" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K75" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L75" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M75" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N75" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O75" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B76" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I76" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="J76" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L76" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M76" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B77" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C77" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I77" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="J77" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L77" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K77" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L77" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M77" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N77" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O77" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B78" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I78" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="J78" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L78" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K78" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L78" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M78" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N78" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O78" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="79" spans="1:16">
       <c r="A79" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B79" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C79" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I79" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="J79" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L79" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K79" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L79" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M79" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N79" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O79" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B80" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>386</v>
+        <v>266</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J80" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L80" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K80" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L80" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M80" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N80" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O80" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="P80" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="81" spans="1:16">
       <c r="A81" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B81" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>386</v>
+        <v>266</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J81" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L81" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="P81" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="82" spans="1:16">
       <c r="A82" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B82" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>386</v>
+        <v>266</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J82" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L82" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K82" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M82" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N82" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O82" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="P82" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B83" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>386</v>
+        <v>266</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J83" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L83" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="P83" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B84" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>386</v>
+        <v>266</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J84" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L84" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K84" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L84" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M84" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N84" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O84" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="P84" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="85" spans="1:16">
       <c r="A85" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B85" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>386</v>
+        <v>266</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J85" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L85" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K85" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L85" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M85" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N85" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O85" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="P85" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="86" spans="1:16">
       <c r="A86" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B86" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>386</v>
+        <v>266</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J86" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L86" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K86" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L86" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M86" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N86" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O86" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="P86" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B87" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>386</v>
+        <v>266</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>383</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J87" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L87" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K87" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L87" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M87" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N87" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O87" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="P87" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B88" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>386</v>
+        <v>266</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>383</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J88" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L88" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K88" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L88" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M88" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N88" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O88" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="P88" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="89" spans="1:16">
       <c r="A89" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B89" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>386</v>
+        <v>266</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>383</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J89" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L89" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="P89" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B90" t="s">
-        <v>255</v>
+        <v>253</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>386</v>
+        <v>266</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>383</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J90" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L90" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K90" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L90" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M90" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N90" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O90" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="P90" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B91" t="s">
         <v>119</v>
       </c>
+      <c r="C91" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="E91" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>386</v>
+        <v>266</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>383</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J91" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L91" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="P91" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B92" t="s">
         <v>119</v>
       </c>
+      <c r="D92" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="E92" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>386</v>
+        <v>266</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>383</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M92" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N92" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O92" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:16">
       <c r="A93" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B93" t="s">
         <v>119</v>
       </c>
+      <c r="D93" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="E93" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M93" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N93" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O93" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P93" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94" spans="1:16">
       <c r="A94" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B94" t="s">
         <v>119</v>
       </c>
+      <c r="D94" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="E94" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P94" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="95" spans="1:16">
       <c r="A95" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B95" t="s">
         <v>119</v>
       </c>
+      <c r="D95" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="E95" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M95" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N95" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O95" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="96" spans="1:16">
       <c r="A96" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B96" t="s">
         <v>119</v>
       </c>
+      <c r="D96" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="E96" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="97" spans="1:16">
       <c r="A97" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B97" t="s">
         <v>119</v>
       </c>
+      <c r="D97" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="E97" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="M97" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="N97" s="3" t="s">
+      <c r="G97" s="3" t="s">
         <v>271</v>
       </c>
+      <c r="L97" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="P97" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="98" spans="1:16">
       <c r="A98" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B98" t="s">
         <v>119</v>
       </c>
+      <c r="D98" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="E98" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="M98" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N98" s="3" t="s">
-        <v>271</v>
+        <v>384</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="99" spans="1:16">
       <c r="A99" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B99" t="s">
         <v>119</v>
       </c>
+      <c r="D99" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="E99" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="M99" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N99" s="3" t="s">
-        <v>271</v>
+        <v>385</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="100" spans="1:16">
       <c r="A100" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B100" t="s">
         <v>119</v>
       </c>
+      <c r="D100" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="E100" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>271</v>
+        <v>385</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="101" spans="1:16">
       <c r="A101" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B101" t="s">
         <v>119</v>
       </c>
+      <c r="D101" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="E101" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>271</v>
+        <v>385</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="P101" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="102" spans="1:16">
       <c r="A102" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B102" t="s">
         <v>119</v>
       </c>
+      <c r="D102" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="E102" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>388</v>
+        <v>275</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="P102" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="103" spans="1:16">
       <c r="A103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B103" t="s">
         <v>119</v>
       </c>
+      <c r="D103" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="E103" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>388</v>
+        <v>275</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M103" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N103" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O103" s="3" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="P103" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="104" spans="1:16">
       <c r="A104" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B104" t="s">
         <v>119</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L104" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="O104" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="P104" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:16">
       <c r="A105" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B105" t="s">
         <v>119</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L105" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="O105" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="J105" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="P105" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="106" spans="1:16">
       <c r="A106" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B106" t="s">
         <v>119</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="L106" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="O106" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="P106" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="107" spans="1:16">
       <c r="A107" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B107" t="s">
         <v>120</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="L107" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="O107" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J107" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="P107" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="108" spans="1:16">
       <c r="A108" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B108" t="s">
         <v>120</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="L108" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="O108" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J108" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="P108" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="109" spans="1:16">
       <c r="A109" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B109" t="s">
         <v>120</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="L109" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="O109" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="P109" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="110" spans="1:16">
       <c r="A110" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B110" t="s">
         <v>120</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="L110" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="O110" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="P110" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="111" spans="1:16">
       <c r="A111" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B111" t="s">
         <v>120</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="L111" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="O111" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J111" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="P111" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="112" spans="1:16">
       <c r="A112" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B112" t="s">
         <v>120</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="L112" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="O112" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="P112" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="113" spans="1:16">
       <c r="A113" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B113" t="s">
         <v>120</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="L113" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="O113" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="P113" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="114" spans="1:16">
       <c r="A114" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B114" t="s">
         <v>120</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="L114" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="O114" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="P114" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="115" spans="1:16">
       <c r="A115" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B115" t="s">
         <v>120</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P115" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="116" spans="1:16">
       <c r="A116" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B116" t="s">
         <v>120</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P116" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="117" spans="1:16">
       <c r="A117" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B117" t="s">
         <v>120</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P117" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="118" spans="1:16">
       <c r="A118" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B118" t="s">
         <v>120</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F118" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P118" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="119" spans="1:16">
       <c r="A119" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B119" t="s">
         <v>120</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P119" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="120" spans="1:16">
       <c r="A120" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B120" t="s">
         <v>120</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P120" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="121" spans="1:16">
       <c r="A121" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B121" t="s">
         <v>120</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P121" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="122" spans="1:16">
       <c r="A122" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B122" t="s">
         <v>120</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P122" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="123" spans="1:16">
       <c r="A123" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B123" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P123" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="124" spans="1:16">
       <c r="A124" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B124" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P124" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="125" spans="1:16">
       <c r="A125" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B125" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F125" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P125" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="126" spans="1:16">
       <c r="A126" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B126" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F126" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P126" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="127" spans="1:16">
       <c r="A127" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B127" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F127" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P127" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="128" spans="1:16">
       <c r="A128" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B128" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F128" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P128" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="129" spans="1:16">
       <c r="A129" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B129" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F129" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P129" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="130" spans="1:16">
       <c r="A130" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B130" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F130" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P130" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="131" spans="1:16">
       <c r="A131" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B131" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F131" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P131" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="132" spans="1:16">
       <c r="A132" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B132" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P132" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="133" spans="1:16">
       <c r="A133" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B133" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F133" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P133" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="134" spans="1:16">
       <c r="A134" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B134" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F134" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P134" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="135" spans="1:16">
       <c r="A135" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B135" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F135" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P135" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="136" spans="1:16">
       <c r="A136" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B136" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F136" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P136" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="137" spans="1:16">
       <c r="A137" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B137" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F137" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P137" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="138" spans="1:16">
       <c r="A138" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B138" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F138" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P138" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="139" spans="1:16">
       <c r="A139" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B139" t="s">
         <v>119</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F139" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P139" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="140" spans="1:16">
       <c r="A140" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B140" t="s">
         <v>119</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F140" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P140" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="141" spans="1:16">
       <c r="A141" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B141" t="s">
         <v>119</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F141" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P141" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="142" spans="1:16">
       <c r="A142" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B142" t="s">
         <v>119</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F142" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P142" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="143" spans="1:16">
       <c r="A143" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B143" t="s">
         <v>119</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F143" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P143" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="144" spans="1:16">
       <c r="A144" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B144" t="s">
         <v>119</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P144" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="145" spans="1:16">
       <c r="A145" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B145" t="s">
         <v>119</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F145" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P145" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="146" spans="1:16">
       <c r="A146" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B146" t="s">
         <v>119</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F146" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P146" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="147" spans="1:16">
       <c r="A147" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B147" t="s">
         <v>119</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P147" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="148" spans="1:16">
       <c r="A148" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B148" t="s">
         <v>119</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F148" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P148" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="149" spans="1:16">
       <c r="A149" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B149" t="s">
         <v>119</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F149" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P149" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="150" spans="1:16">
       <c r="A150" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B150" t="s">
         <v>119</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P150" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="151" spans="1:16">
       <c r="A151" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B151" t="s">
         <v>119</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F151" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P151" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="152" spans="1:16">
       <c r="A152" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B152" t="s">
         <v>119</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F152" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P152" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="153" spans="1:16">
       <c r="A153" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B153" t="s">
         <v>119</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F153" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P153" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="154" spans="1:16">
       <c r="A154" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B154" t="s">
         <v>119</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F154" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P154" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="155" spans="1:16">
       <c r="A155" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B155" t="s">
         <v>120</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F155" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P155" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="156" spans="1:16">
       <c r="A156" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B156" t="s">
         <v>120</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P156" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="157" spans="1:16">
       <c r="A157" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B157" t="s">
         <v>120</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P157" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="158" spans="1:16">
       <c r="A158" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B158" t="s">
         <v>120</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F158" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P158" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="159" spans="1:16">
       <c r="A159" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B159" t="s">
         <v>120</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F159" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P159" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="160" spans="1:16">
       <c r="A160" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B160" t="s">
         <v>120</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F160" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P160" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="161" spans="1:16">
       <c r="A161" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B161" t="s">
         <v>120</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P161" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:16">
       <c r="A162" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B162" t="s">
         <v>120</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F162" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P162" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="163" spans="1:16">
       <c r="A163" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B163" t="s">
         <v>120</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P163" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="164" spans="1:16">
       <c r="A164" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B164" t="s">
         <v>120</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F164" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P164" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="165" spans="1:16">
       <c r="A165" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B165" t="s">
         <v>120</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F165" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P165" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="166" spans="1:16">
       <c r="A166" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B166" t="s">
         <v>120</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F166" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P166" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="167" spans="1:16">
       <c r="A167" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B167" t="s">
         <v>120</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F167" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P167" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="168" spans="1:16">
       <c r="A168" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B168" t="s">
         <v>120</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F168" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P168" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="169" spans="1:16">
       <c r="A169" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B169" t="s">
         <v>120</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F169" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P169" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="170" spans="1:16">
       <c r="A170" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B170" t="s">
         <v>120</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F170" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P170" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="171" spans="1:16">
       <c r="A171" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B171" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F171" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P171" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="172" spans="1:16">
       <c r="A172" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B172" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F172" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P172" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="173" spans="1:16">
       <c r="A173" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B173" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F173" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P173" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="174" spans="1:16">
       <c r="A174" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B174" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F174" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P174" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="175" spans="1:16">
       <c r="A175" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B175" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F175" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P175" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="176" spans="1:16">
       <c r="A176" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B176" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F176" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P176" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="177" spans="1:16">
       <c r="A177" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B177" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F177" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P177" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="178" spans="1:16">
       <c r="A178" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B178" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F178" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P178" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="179" spans="1:16">
       <c r="A179" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B179" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F179" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P179" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="180" spans="1:16">
       <c r="A180" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B180" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F180" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P180" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="181" spans="1:16">
       <c r="A181" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B181" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F181" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P181" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="182" spans="1:16">
       <c r="A182" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B182" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F182" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P182" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="183" spans="1:16">
       <c r="A183" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B183" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F183" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P183" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="184" spans="1:16">
       <c r="A184" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B184" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P184" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="185" spans="1:16">
       <c r="A185" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B185" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F185" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P185" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="186" spans="1:16">
       <c r="A186" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B186" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F186" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P186" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="187" spans="1:16">
       <c r="A187" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B187" t="s">
         <v>119</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F187" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="P187" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="188" spans="1:16">
       <c r="A188" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B188" t="s">
         <v>119</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F188" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="189" spans="1:16">
       <c r="A189" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B189" t="s">
         <v>119</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F189" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="190" spans="1:16">
       <c r="A190" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B190" t="s">
         <v>119</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F190" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="191" spans="1:16">
       <c r="A191" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B191" t="s">
         <v>119</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F191" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="192" spans="1:16">
       <c r="A192" t="s">
+        <v>375</v>
+      </c>
+      <c r="B192" t="s">
+        <v>119</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" t="s">
         <v>376</v>
       </c>
-      <c r="B192" t="s">
-        <v>119</v>
-      </c>
-      <c r="E192" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F192" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
-      <c r="A193" t="s">
+      <c r="B193" t="s">
+        <v>119</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" t="s">
         <v>377</v>
       </c>
-      <c r="B193" t="s">
-        <v>119</v>
-      </c>
-      <c r="E193" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F193" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194" t="s">
+      <c r="B194" t="s">
+        <v>119</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" t="s">
         <v>378</v>
       </c>
-      <c r="B194" t="s">
-        <v>119</v>
-      </c>
-      <c r="E194" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F194" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6">
-      <c r="A195" t="s">
+      <c r="B195" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" t="s">
         <v>379</v>
       </c>
-      <c r="B195" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
-      <c r="A196" t="s">
+      <c r="B196" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" t="s">
         <v>380</v>
       </c>
-      <c r="B196" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
-      <c r="A197" t="s">
+      <c r="B197" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" t="s">
         <v>381</v>
-      </c>
-      <c r="B197" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6">
-      <c r="A198" t="s">
-        <v>382</v>
       </c>
       <c r="B198" t="s">
         <v>119</v>
@@ -9129,34 +8868,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -9164,7 +8903,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C2" t="s">
         <v>76</v>
@@ -9190,7 +8929,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C3" t="s">
         <v>77</v>
@@ -9216,7 +8955,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -9242,7 +8981,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C5" t="s">
         <v>79</v>
@@ -9268,7 +9007,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C6" t="s">
         <v>80</v>
@@ -9294,7 +9033,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C7" t="s">
         <v>81</v>
@@ -9320,7 +9059,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C8" t="s">
         <v>82</v>
@@ -9346,7 +9085,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C9" t="s">
         <v>83</v>
@@ -9372,7 +9111,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C10" t="s">
         <v>84</v>
@@ -9398,7 +9137,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C11" t="s">
         <v>85</v>
@@ -9424,7 +9163,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C12" t="s">
         <v>86</v>
@@ -9450,7 +9189,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C13" t="s">
         <v>87</v>
@@ -9476,7 +9215,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C14" t="s">
         <v>88</v>
@@ -9502,7 +9241,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C15" t="s">
         <v>89</v>
@@ -9528,7 +9267,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C16" t="s">
         <v>90</v>
@@ -9554,7 +9293,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C17" t="s">
         <v>91</v>
@@ -9580,7 +9319,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C18" t="s">
         <v>92</v>
@@ -9606,7 +9345,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C19" t="s">
         <v>93</v>
@@ -9632,7 +9371,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C20" t="s">
         <v>94</v>
@@ -9658,7 +9397,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C21" t="s">
         <v>95</v>
@@ -9684,7 +9423,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C22" t="s">
         <v>96</v>
@@ -9710,7 +9449,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C23" t="s">
         <v>97</v>
@@ -9736,7 +9475,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C24" t="s">
         <v>98</v>
@@ -9762,7 +9501,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C25" t="s">
         <v>99</v>
@@ -9788,7 +9527,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C26" t="s">
         <v>100</v>
@@ -9814,7 +9553,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C27" t="s">
         <v>101</v>
@@ -9840,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C28" t="s">
         <v>102</v>
@@ -9866,7 +9605,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C29" t="s">
         <v>103</v>
